--- a/data/b2_candoi/B2 Candói 11-2025.xlsx
+++ b/data/b2_candoi/B2 Candói 11-2025.xlsx
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1036.21</v>
+        <v>983.78</v>
       </c>
     </row>
     <row r="3">
@@ -4743,12 +4743,12 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57551.64</v>
+        <v>56615.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45970</v>
+        <v>45966</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -4757,11 +4757,11 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1503.06</v>
+        <v>1783.09</v>
       </c>
     </row>
     <row r="5">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3867.45</v>
+        <v>3538.82</v>
       </c>
     </row>
     <row r="6">
@@ -4802,20 +4802,20 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1438.19</v>
+        <v>2904.74</v>
       </c>
     </row>
     <row r="8">
@@ -4833,25 +4833,25 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1078.41</v>
+        <v>1138.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45975</v>
+        <v>45976</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1032.22</v>
+        <v>8550.48</v>
       </c>
     </row>
     <row r="10">
@@ -4860,16 +4860,16 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>7287.62</v>
+        <v>1144.08</v>
       </c>
     </row>
     <row r="11">
@@ -4878,16 +4878,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1064.09</v>
+        <v>922.3</v>
       </c>
     </row>
     <row r="12">
@@ -4896,88 +4896,88 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3560.05</v>
+        <v>928.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>45979</v>
+        <v>45977</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1078.66</v>
+        <v>3705.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45981</v>
+        <v>45979</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>20454.11</v>
+        <v>1277.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45984</v>
+        <v>45981</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3793.08</v>
+        <v>20305.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45986</v>
+        <v>45984</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>7920</v>
+        <v>3750.31</v>
       </c>
     </row>
     <row r="17">
@@ -4986,16 +4986,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1948.76</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="18">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3810.91</v>
+        <v>3856.49</v>
       </c>
     </row>
   </sheetData>
